--- a/data/trans_orig/P79$hipoteca_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79$hipoteca_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23602</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>34831</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>16832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24589</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>294199</t>
+          <t>301432</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276741</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300638</t>
+          <t>306574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>276390</t>
+          <t>302593</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257193</t>
+          <t>290408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>281843</t>
+          <t>306553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>570589</t>
+          <t>604026</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>549737</t>
+          <t>590234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>580947</t>
+          <t>611829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>18315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>26017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33954</t>
+          <t>31263</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2424,17 +2424,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2537,69 +2537,69 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34717</t>
+          <t>37047</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>24626</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>17200</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>36614</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>22592</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>14314</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>32173</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>47</t>
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32087</t>
+          <t>34138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61385</t>
+          <t>63749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46536</t>
+          <t>45105</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>43478</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29537</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60100</t>
+          <t>61660</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>448110</t>
+          <t>459610</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>426926</t>
+          <t>438993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>465634</t>
+          <t>476015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>458538</t>
+          <t>485727</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>445901</t>
+          <t>470590</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>468476</t>
+          <t>496574</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>906648</t>
+          <t>945337</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>881778</t>
+          <t>920694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>926538</t>
+          <t>964318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>865</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,22 +3480,22 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3671,32 +3671,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14343</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3784,32 +3784,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3819,32 +3819,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29259</t>
+          <t>27376</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>28439</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>18983</t>
+          <t>19518</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39690</t>
+          <t>39653</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>296627</t>
+          <t>294144</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>287893</t>
+          <t>284055</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>303231</t>
+          <t>301338</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,67 +4384,67 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>313096</t>
+          <t>319702</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>302043</t>
+          <t>309887</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>320622</t>
+          <t>326884</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
+          <t>95,37%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>613846</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>601917</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>625184</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>95,45%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>609723</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>596489</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>619692</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>18151</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>25386</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4805,69 +4805,69 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4062</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>3917</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16023</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,22 +4953,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8512</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>29615</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>39524</t>
+          <t>47269</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>26493</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>56147</t>
+          <t>69996</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>265398</t>
+          <t>308120</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>246948</t>
+          <t>286829</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>276468</t>
+          <t>323372</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>350001</t>
+          <t>354687</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>337047</t>
+          <t>339534</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>359917</t>
+          <t>365397</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>615400</t>
+          <t>662807</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>595952</t>
+          <t>635853</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>633079</t>
+          <t>680928</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5861,32 +5861,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>441</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>443</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>378</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6313,32 +6313,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>825</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>174135</t>
+          <t>199317</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>170277</t>
+          <t>195128</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>175647</t>
+          <t>201347</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>249783</t>
+          <t>219057</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>245576</t>
+          <t>214467</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>252006</t>
+          <t>221679</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>423918</t>
+          <t>418374</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>418461</t>
+          <t>413038</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>426777</t>
+          <t>421774</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7108,32 +7108,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7143,32 +7143,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7256,32 +7256,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>700</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7482,32 +7482,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -7525,32 +7525,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7560,32 +7560,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>21668</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7595,32 +7595,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>18817</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>37611</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7977,32 +7977,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8047,32 +8047,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -8090,32 +8090,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>253573</t>
+          <t>250026</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>244852</t>
+          <t>241885</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>258299</t>
+          <t>255925</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>240510</t>
+          <t>244199</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>233098</t>
+          <t>236334</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>245756</t>
+          <t>250082</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>494083</t>
+          <t>494224</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>484218</t>
+          <t>483051</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>501544</t>
+          <t>502576</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -8207,22 +8207,22 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -8320,32 +8320,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8355,32 +8355,32 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>27115</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8390,32 +8390,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>35502</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -8433,32 +8433,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8468,32 +8468,32 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8503,27 +8503,27 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8581,32 +8581,32 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8616,27 +8616,27 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8659,32 +8659,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8694,32 +8694,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8729,32 +8729,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>18075</t>
+          <t>18379</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -8772,32 +8772,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>31319</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8807,32 +8807,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>36936</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>56416</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8842,32 +8842,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>64508</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>31375</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>70823</t>
+          <t>83661</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>708</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9146,32 +9146,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>869</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -9224,32 +9224,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9259,32 +9259,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>20287</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -9337,32 +9337,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>561813</t>
+          <t>647412</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>550026</t>
+          <t>633620</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>571609</t>
+          <t>657652</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,32 +9372,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>760531</t>
+          <t>659733</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>733566</t>
+          <t>642563</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>793665</t>
+          <t>673792</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>1322343</t>
+          <t>1307145</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1296869</t>
+          <t>1287018</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>1354950</t>
+          <t>1326336</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -9454,32 +9454,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>34968</t>
+          <t>36293</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9489,32 +9489,32 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9524,32 +9524,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>48528</t>
+          <t>52384</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -9567,32 +9567,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>40972</t>
+          <t>52709</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9602,32 +9602,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17583</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>37839</t>
+          <t>44797</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9637,32 +9637,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>68957</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>71198</t>
+          <t>89261</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9750,32 +9750,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -9803,12 +9803,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
@@ -9873,12 +9873,12 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -9906,32 +9906,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9941,32 +9941,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>27518</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9976,32 +9976,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>18803</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>53334</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -10019,32 +10019,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>172790</t>
+          <t>203633</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>90286</t>
+          <t>179357</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>245475</t>
+          <t>229772</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10054,32 +10054,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>186875</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>168784</t>
+          <t>194568</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>209958</t>
+          <t>239054</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10089,32 +10089,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>359665</t>
+          <t>419409</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>219890</t>
+          <t>386541</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>440421</t>
+          <t>449832</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -10132,32 +10132,32 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10202,32 +10202,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -10280,32 +10280,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>801</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10315,32 +10315,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -10393,32 +10393,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>743</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10428,32 +10428,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -10471,32 +10471,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>106478</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>89197</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>133983</t>
+          <t>128079</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10506,32 +10506,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>86685</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>73175</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>103193</t>
+          <t>117223</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10541,32 +10541,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>179506</t>
+          <t>206436</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>108774</t>
+          <t>182824</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>221441</t>
+          <t>232947</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -10584,32 +10584,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>660035</t>
+          <t>479572</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>554712</t>
+          <t>449431</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>778010</t>
+          <t>508044</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10619,67 +10619,67 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>425470</t>
+          <t>494518</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>402581</t>
+          <t>469074</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>447619</t>
+          <t>517187</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
+          <t>61,73%</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>58,56%</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>64,56%</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>974090</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>938712</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>1012295</t>
+        </is>
+      </c>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
           <t>61,59%</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>58,28%</t>
-        </is>
-      </c>
-      <c r="P91" s="2" t="inlineStr">
-        <is>
-          <t>64,8%</t>
-        </is>
-      </c>
-      <c r="Q91" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="R91" s="2" t="inlineStr">
-        <is>
-          <t>1085506</t>
-        </is>
-      </c>
-      <c r="S91" s="2" t="inlineStr">
-        <is>
-          <t>976794</t>
-        </is>
-      </c>
-      <c r="T91" s="2" t="inlineStr">
-        <is>
-          <t>1304035</t>
-        </is>
-      </c>
-      <c r="U91" s="2" t="inlineStr">
-        <is>
-          <t>67,59%</t>
-        </is>
-      </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -10701,32 +10701,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10736,32 +10736,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10771,32 +10771,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>46623</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>77646</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -10814,32 +10814,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>65621</t>
+          <t>85539</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10849,32 +10849,32 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>48871</t>
+          <t>67680</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>87640</t>
+          <t>105514</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10884,32 +10884,32 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>90124</t>
+          <t>125300</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>146012</t>
+          <t>178156</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -10927,32 +10927,32 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>40581</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10962,32 +10962,32 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>26817</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10997,32 +10997,32 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>58984</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -11040,17 +11040,17 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11075,17 +11075,17 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>59263</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>53784</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>64779</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>100895</t>
+          <t>114533</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -11266,32 +11266,32 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>195743</t>
+          <t>261531</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>289261</t>
+          <t>331263</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11301,32 +11301,32 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>252569</t>
+          <t>322238</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>344051</t>
+          <t>385949</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11336,32 +11336,32 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>481189</t>
+          <t>599265</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>618283</t>
+          <t>697938</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -11379,32 +11379,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11414,67 +11414,67 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>13530</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>33057</t>
+        </is>
+      </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P98" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q98" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R98" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
-        </is>
-      </c>
-      <c r="S98" s="2" t="inlineStr">
-        <is>
-          <t>11330</t>
-        </is>
-      </c>
-      <c r="T98" s="2" t="inlineStr">
-        <is>
-          <t>29347</t>
-        </is>
-      </c>
-      <c r="U98" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V98" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -11527,22 +11527,22 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11562,22 +11562,22 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V99" s="2" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11640,67 +11640,67 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
           <t>0,03%</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q100" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R100" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="S100" s="2" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="T100" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="U100" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V100" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -11718,32 +11718,32 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>102394</t>
+          <t>128918</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11753,32 +11753,32 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>103192</t>
+          <t>124725</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>149760</t>
+          <t>167612</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11788,32 +11788,32 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>226127</t>
+          <t>271095</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>303138</t>
+          <t>340065</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -11831,32 +11831,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2953890</t>
+          <t>2939631</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>2895118</t>
+          <t>2894495</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>3042585</t>
+          <t>2985086</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11866,32 +11866,32 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>3074321</t>
+          <t>3080217</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>3028389</t>
+          <t>3039780</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>3148028</t>
+          <t>3117324</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11901,32 +11901,32 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>6028210</t>
+          <t>6019848</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>5945894</t>
+          <t>5961646</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>6138405</t>
+          <t>6077518</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
